--- a/data/employees/EMP060/AST-EMP060-06.xlsx
+++ b/data/employees/EMP060/AST-EMP060-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Skyler Chen (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Skyler Chen | Role: Analyst | Location: Hsinchu | Date: 2025-03-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>99</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>98</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>98</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>84</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>97</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>60</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Fabric semantic model planning. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>82</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>66</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>82</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>85</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>71</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>96</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>88</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>76</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>86</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>91</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>83</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>75</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp060 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>84</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP060</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP060 contributes to ast emp060 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>